--- a/resultados/saojoaodoivai/inventario_links.xlsx
+++ b/resultados/saojoaodoivai/inventario_links.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1971,6 +1971,76 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>saojoaodoivai</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>https://saojoaodoivai.eloweb.net/portaltransparencia-api/api/files/ajuda</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>saojoaodoivai.eloweb.net</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" t="n">
+        <v>200</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2026-08-15 11:17:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>saojoaodoivai</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>https://saojoaodoivai.eloweb.net/portaltransparencia-api/v3/api-docs</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>saojoaodoivai.eloweb.net</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>.json</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>2</v>
+      </c>
+      <c r="H39" t="n">
+        <v>200</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2026-08-15 11:32:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
